--- a/product_selector_out/STM32WBA6x.xlsx
+++ b/product_selector_out/STM32WBA6x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7808,9 +7808,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7823,17 +7823,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7848,7 +7848,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7858,12 +7858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7873,14 +7873,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -7898,27 +7898,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7933,22 +7933,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7958,7 +7958,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7983,7 +7983,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8008,7 +8008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8018,12 +8018,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8033,22 +8033,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="8" t="inlineStr">
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8073,7 +8073,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF12" s="8" t="inlineStr">
+      <c r="BF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8083,12 +8083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8103,12 +8103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8123,9 +8123,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8150,9 +8150,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -8165,17 +8165,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8190,7 +8190,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8200,12 +8200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8215,14 +8215,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -8240,27 +8240,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8275,22 +8275,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8300,7 +8300,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8325,7 +8325,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8350,7 +8350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8360,12 +8360,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8375,22 +8375,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="8" t="inlineStr">
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8415,7 +8415,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="8" t="inlineStr">
+      <c r="BF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8425,12 +8425,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8445,12 +8445,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8465,9 +8465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8492,9 +8492,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8507,17 +8507,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8532,7 +8532,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8542,12 +8542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8557,14 +8557,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -8582,27 +8582,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8617,22 +8617,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8642,7 +8642,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8667,7 +8667,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8692,7 +8692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8702,12 +8702,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8717,22 +8717,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="8" t="inlineStr">
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8757,7 +8757,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="8" t="inlineStr">
+      <c r="BF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8767,12 +8767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8787,12 +8787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8807,9 +8807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8834,9 +8834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8849,17 +8849,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8874,7 +8874,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8884,29 +8884,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -8919,62 +8919,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8984,32 +8984,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9034,7 +9034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9044,47 +9044,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9099,7 +9099,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF15" s="8" t="inlineStr">
+      <c r="BF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9109,12 +9109,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9129,12 +9129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9149,9 +9149,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9191,17 +9191,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9216,7 +9216,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9226,12 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9241,14 +9241,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -9266,27 +9266,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9301,22 +9301,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9326,7 +9326,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9351,7 +9351,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9376,7 +9376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9386,12 +9386,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9401,22 +9401,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="8" t="inlineStr">
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9441,7 +9441,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="8" t="inlineStr">
+      <c r="BF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9451,12 +9451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9471,12 +9471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9491,9 +9491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9518,9 +9518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -9533,17 +9533,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9558,7 +9558,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9568,29 +9568,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -9603,62 +9603,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9668,7 +9668,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9693,7 +9693,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9718,7 +9718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9728,37 +9728,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9783,7 +9783,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF17" s="8" t="inlineStr">
+      <c r="BF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9793,12 +9793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9813,12 +9813,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9833,9 +9833,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9875,17 +9875,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9900,7 +9900,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9910,12 +9910,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9950,27 +9950,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9985,22 +9985,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10010,7 +10010,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10035,7 +10035,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10060,7 +10060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10070,12 +10070,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10090,17 +10090,17 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="8" t="inlineStr">
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10125,7 +10125,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="8" t="inlineStr">
+      <c r="BF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10135,12 +10135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10155,12 +10155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10202,9 +10202,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10217,17 +10217,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10242,7 +10242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10252,29 +10252,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -10287,62 +10287,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10352,7 +10352,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10377,7 +10377,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10402,7 +10402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10412,37 +10412,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10467,7 +10467,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="8" t="inlineStr">
+      <c r="BF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10477,12 +10477,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10497,12 +10497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10517,9 +10517,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10544,9 +10544,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10559,17 +10559,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10584,7 +10584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10594,12 +10594,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10609,14 +10609,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10634,27 +10634,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10669,22 +10669,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10694,7 +10694,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10719,7 +10719,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10744,7 +10744,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10754,12 +10754,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10769,22 +10769,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="8" t="inlineStr">
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10809,7 +10809,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF20" s="8" t="inlineStr">
+      <c r="BF20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10819,12 +10819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10839,12 +10839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10859,9 +10859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10886,9 +10886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10901,17 +10901,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10926,7 +10926,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10936,29 +10936,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -10971,62 +10971,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11036,32 +11036,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11086,7 +11086,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11096,47 +11096,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11151,7 +11151,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="8" t="inlineStr">
+      <c r="BF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11161,12 +11161,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11181,12 +11181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11201,9 +11201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11228,9 +11228,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11243,17 +11243,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11268,7 +11268,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11278,12 +11278,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11293,14 +11293,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -11318,27 +11318,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11353,22 +11353,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11378,7 +11378,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11403,7 +11403,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11428,7 +11428,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11438,37 +11438,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11493,7 +11493,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="8" t="inlineStr">
+      <c r="BF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11503,12 +11503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11523,12 +11523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11543,9 +11543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11570,9 +11570,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11585,17 +11585,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11610,7 +11610,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11620,12 +11620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11635,14 +11635,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11660,57 +11660,57 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11720,32 +11720,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11770,7 +11770,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11780,37 +11780,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11835,7 +11835,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="8" t="inlineStr">
+      <c r="BF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11845,12 +11845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11865,12 +11865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11885,9 +11885,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11912,9 +11912,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11927,17 +11927,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11952,7 +11952,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11962,12 +11962,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11977,14 +11977,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12002,27 +12002,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12037,22 +12037,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12062,7 +12062,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12087,7 +12087,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12112,7 +12112,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12122,12 +12122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12137,22 +12137,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="8" t="inlineStr">
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12177,7 +12177,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="8" t="inlineStr">
+      <c r="BF24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12187,12 +12187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12207,12 +12207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12254,9 +12254,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12269,17 +12269,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12294,7 +12294,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12304,29 +12304,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -12339,62 +12339,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12404,32 +12404,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12454,7 +12454,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12464,47 +12464,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12519,7 +12519,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="8" t="inlineStr">
+      <c r="BF25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12529,12 +12529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12549,12 +12549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12596,9 +12596,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12611,17 +12611,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12636,7 +12636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12646,12 +12646,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12661,14 +12661,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12686,27 +12686,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA26" s="8" t="inlineStr">
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12721,22 +12721,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12746,7 +12746,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12771,7 +12771,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="8" t="inlineStr">
+      <c r="AN26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12796,7 +12796,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="8" t="inlineStr">
+      <c r="AS26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12806,12 +12806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="8" t="inlineStr">
+      <c r="AU26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12821,22 +12821,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA26" s="8" t="inlineStr">
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12861,7 +12861,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF26" s="8" t="inlineStr">
+      <c r="BF26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12871,12 +12871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="8" t="inlineStr">
+      <c r="BH26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12891,12 +12891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="8" t="inlineStr">
+      <c r="BL26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12911,9 +12911,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12938,9 +12938,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12953,17 +12953,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12978,7 +12978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12988,12 +12988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13003,14 +13003,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -13028,27 +13028,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA27" s="8" t="inlineStr">
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13063,22 +13063,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="8" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13088,7 +13088,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13113,7 +13113,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="inlineStr">
+      <c r="AN27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13138,7 +13138,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="8" t="inlineStr">
+      <c r="AS27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13148,12 +13148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="8" t="inlineStr">
+      <c r="AU27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13163,22 +13163,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA27" s="8" t="inlineStr">
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13203,7 +13203,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF27" s="8" t="inlineStr">
+      <c r="BF27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13213,12 +13213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="8" t="inlineStr">
+      <c r="BH27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13233,12 +13233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="8" t="inlineStr">
+      <c r="BL27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13253,9 +13253,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13280,9 +13280,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13295,17 +13295,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13320,7 +13320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13330,12 +13330,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13345,14 +13345,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13370,27 +13370,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA28" s="8" t="inlineStr">
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13405,22 +13405,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG28" s="8" t="inlineStr">
+      <c r="AD28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13430,7 +13430,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="8" t="inlineStr">
+      <c r="AI28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13455,7 +13455,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN28" s="8" t="inlineStr">
+      <c r="AN28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13480,7 +13480,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS28" s="8" t="inlineStr">
+      <c r="AS28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13490,12 +13490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV28" s="8" t="inlineStr">
+      <c r="AU28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13505,22 +13505,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA28" s="8" t="inlineStr">
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13545,7 +13545,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF28" s="8" t="inlineStr">
+      <c r="BF28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13555,12 +13555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI28" s="8" t="inlineStr">
+      <c r="BH28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13575,12 +13575,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM28" s="8" t="inlineStr">
+      <c r="BL28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13595,9 +13595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13622,9 +13622,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13637,17 +13637,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13662,7 +13662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13672,29 +13672,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -13707,62 +13707,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="8" t="inlineStr">
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13772,7 +13772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="8" t="inlineStr">
+      <c r="AI29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13797,7 +13797,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN29" s="8" t="inlineStr">
+      <c r="AN29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13822,7 +13822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS29" s="8" t="inlineStr">
+      <c r="AS29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13832,37 +13832,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AZ29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA29" s="8" t="inlineStr">
+      <c r="AU29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13887,7 +13887,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF29" s="8" t="inlineStr">
+      <c r="BF29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13897,12 +13897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI29" s="8" t="inlineStr">
+      <c r="BH29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13917,12 +13917,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM29" s="8" t="inlineStr">
+      <c r="BL29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13937,9 +13937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13992,7 +13992,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14036,7 +14036,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14051,19 +14051,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WBA65CI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14073,1107 +14073,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WBA6x.xlsx
+++ b/product_selector_out/STM32WBA6x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -7808,9 +7808,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7823,17 +7823,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7848,7 +7848,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7858,12 +7858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7873,14 +7873,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -7898,27 +7898,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7933,22 +7933,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7958,7 +7958,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7983,7 +7983,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="7" t="inlineStr">
+      <c r="AN12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8008,7 +8008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="7" t="inlineStr">
+      <c r="AS12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8018,12 +8018,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8033,22 +8033,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="7" t="inlineStr">
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8073,7 +8073,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF12" s="7" t="inlineStr">
+      <c r="BF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8083,12 +8083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8103,12 +8103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="7" t="inlineStr">
+      <c r="BL12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8123,9 +8123,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8150,9 +8150,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -8165,17 +8165,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8190,7 +8190,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8200,12 +8200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8215,14 +8215,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -8240,27 +8240,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8275,22 +8275,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8300,7 +8300,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8325,7 +8325,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="7" t="inlineStr">
+      <c r="AN13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8350,7 +8350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="7" t="inlineStr">
+      <c r="AS13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8360,12 +8360,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8375,22 +8375,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="7" t="inlineStr">
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8415,7 +8415,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="7" t="inlineStr">
+      <c r="BF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8425,12 +8425,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8445,12 +8445,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="7" t="inlineStr">
+      <c r="BL13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8465,9 +8465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8492,9 +8492,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8507,17 +8507,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8532,7 +8532,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8542,12 +8542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8557,14 +8557,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -8582,27 +8582,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8617,22 +8617,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8642,7 +8642,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8667,7 +8667,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="7" t="inlineStr">
+      <c r="AN14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8692,7 +8692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="7" t="inlineStr">
+      <c r="AS14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8702,12 +8702,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8717,22 +8717,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="7" t="inlineStr">
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8757,7 +8757,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="7" t="inlineStr">
+      <c r="BF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8767,12 +8767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8787,12 +8787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="7" t="inlineStr">
+      <c r="BL14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8807,9 +8807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8834,9 +8834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8849,17 +8849,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8874,7 +8874,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8884,29 +8884,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -8919,62 +8919,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8984,32 +8984,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9034,7 +9034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="7" t="inlineStr">
+      <c r="AS15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9044,47 +9044,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC15" s="7" t="inlineStr">
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9099,7 +9099,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF15" s="7" t="inlineStr">
+      <c r="BF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9109,12 +9109,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9129,12 +9129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="7" t="inlineStr">
+      <c r="BL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9149,9 +9149,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9191,17 +9191,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9216,7 +9216,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9226,12 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9241,14 +9241,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -9266,27 +9266,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9301,22 +9301,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9326,7 +9326,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9351,7 +9351,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="7" t="inlineStr">
+      <c r="AN16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9376,7 +9376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="7" t="inlineStr">
+      <c r="AS16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9386,12 +9386,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9401,22 +9401,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="7" t="inlineStr">
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9441,7 +9441,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="7" t="inlineStr">
+      <c r="BF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9451,12 +9451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9471,12 +9471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="7" t="inlineStr">
+      <c r="BL16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9491,9 +9491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9518,9 +9518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -9533,17 +9533,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9558,7 +9558,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9568,29 +9568,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -9603,62 +9603,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9668,7 +9668,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9693,7 +9693,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="7" t="inlineStr">
+      <c r="AN17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9718,7 +9718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="7" t="inlineStr">
+      <c r="AS17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9728,37 +9728,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="7" t="inlineStr">
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9783,7 +9783,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF17" s="7" t="inlineStr">
+      <c r="BF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9793,12 +9793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9813,12 +9813,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="7" t="inlineStr">
+      <c r="BL17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9833,9 +9833,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9875,17 +9875,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9900,7 +9900,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9910,12 +9910,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9950,27 +9950,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9985,22 +9985,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="7" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10010,7 +10010,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10035,7 +10035,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="7" t="inlineStr">
+      <c r="AN18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10060,7 +10060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="7" t="inlineStr">
+      <c r="AS18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10070,12 +10070,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="7" t="inlineStr">
+      <c r="AU18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10095,12 +10095,12 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AZ18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="7" t="inlineStr">
+      <c r="AZ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10125,7 +10125,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="7" t="inlineStr">
+      <c r="BF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10135,12 +10135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10155,12 +10155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="7" t="inlineStr">
+      <c r="BL18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10202,9 +10202,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10217,17 +10217,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10242,7 +10242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10252,29 +10252,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -10287,62 +10287,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10352,7 +10352,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10377,7 +10377,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="7" t="inlineStr">
+      <c r="AN19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10402,7 +10402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="7" t="inlineStr">
+      <c r="AS19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10412,37 +10412,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="7" t="inlineStr">
+      <c r="AU19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10467,7 +10467,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="7" t="inlineStr">
+      <c r="BF19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10477,12 +10477,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10497,12 +10497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="7" t="inlineStr">
+      <c r="BL19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10517,9 +10517,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10544,9 +10544,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10559,17 +10559,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10584,7 +10584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10594,12 +10594,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10609,14 +10609,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10634,27 +10634,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10669,22 +10669,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="7" t="inlineStr">
+      <c r="AD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10694,7 +10694,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10719,7 +10719,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="7" t="inlineStr">
+      <c r="AN20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10744,7 +10744,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="7" t="inlineStr">
+      <c r="AS20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10754,12 +10754,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="7" t="inlineStr">
+      <c r="AU20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10769,22 +10769,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="7" t="inlineStr">
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10809,7 +10809,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF20" s="7" t="inlineStr">
+      <c r="BF20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10819,12 +10819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10839,12 +10839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="7" t="inlineStr">
+      <c r="BL20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10859,9 +10859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10886,9 +10886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10901,17 +10901,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10926,7 +10926,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10936,29 +10936,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -10971,62 +10971,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="7" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11036,32 +11036,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11086,7 +11086,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="7" t="inlineStr">
+      <c r="AS21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11096,47 +11096,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC21" s="7" t="inlineStr">
+      <c r="AU21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11151,7 +11151,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="7" t="inlineStr">
+      <c r="BF21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11161,12 +11161,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11181,12 +11181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="7" t="inlineStr">
+      <c r="BL21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11201,9 +11201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11228,9 +11228,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11243,17 +11243,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11268,7 +11268,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11278,12 +11278,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11293,14 +11293,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -11318,27 +11318,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="7" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11353,22 +11353,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="7" t="inlineStr">
+      <c r="AD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11378,7 +11378,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11403,7 +11403,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="7" t="inlineStr">
+      <c r="AN22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11428,7 +11428,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="7" t="inlineStr">
+      <c r="AS22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11438,37 +11438,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="7" t="inlineStr">
+      <c r="AU22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11493,7 +11493,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="7" t="inlineStr">
+      <c r="BF22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11503,12 +11503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11523,12 +11523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="7" t="inlineStr">
+      <c r="BL22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11543,9 +11543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11570,9 +11570,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11585,17 +11585,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11610,7 +11610,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11620,12 +11620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11635,14 +11635,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11660,57 +11660,57 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="7" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11720,32 +11720,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11770,7 +11770,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="7" t="inlineStr">
+      <c r="AS23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11780,37 +11780,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="7" t="inlineStr">
+      <c r="AU23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11835,7 +11835,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="7" t="inlineStr">
+      <c r="BF23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11845,12 +11845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11865,12 +11865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="7" t="inlineStr">
+      <c r="BL23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11885,9 +11885,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11912,9 +11912,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11927,17 +11927,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11952,7 +11952,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11962,12 +11962,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11977,14 +11977,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12002,27 +12002,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="7" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12037,22 +12037,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="7" t="inlineStr">
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12062,7 +12062,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12087,7 +12087,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="7" t="inlineStr">
+      <c r="AN24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12112,7 +12112,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="7" t="inlineStr">
+      <c r="AS24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12122,12 +12122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="7" t="inlineStr">
+      <c r="AU24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12137,22 +12137,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="7" t="inlineStr">
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12177,7 +12177,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="7" t="inlineStr">
+      <c r="BF24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12187,12 +12187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="7" t="inlineStr">
+      <c r="BH24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12207,12 +12207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="7" t="inlineStr">
+      <c r="BL24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12254,9 +12254,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12269,17 +12269,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12294,7 +12294,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12304,29 +12304,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -12339,62 +12339,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="7" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12404,32 +12404,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12454,7 +12454,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="7" t="inlineStr">
+      <c r="AS25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12464,47 +12464,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC25" s="7" t="inlineStr">
+      <c r="AU25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12519,7 +12519,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="7" t="inlineStr">
+      <c r="BF25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12529,12 +12529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="7" t="inlineStr">
+      <c r="BH25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12549,12 +12549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="7" t="inlineStr">
+      <c r="BL25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12596,9 +12596,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12611,17 +12611,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12636,7 +12636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12646,12 +12646,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12661,14 +12661,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12686,27 +12686,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA26" s="7" t="inlineStr">
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12721,22 +12721,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="7" t="inlineStr">
+      <c r="AD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12746,7 +12746,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="7" t="inlineStr">
+      <c r="AI26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12771,7 +12771,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="7" t="inlineStr">
+      <c r="AN26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12796,7 +12796,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="7" t="inlineStr">
+      <c r="AS26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12806,12 +12806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="7" t="inlineStr">
+      <c r="AU26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12821,22 +12821,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA26" s="7" t="inlineStr">
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12861,7 +12861,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF26" s="7" t="inlineStr">
+      <c r="BF26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12871,12 +12871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="7" t="inlineStr">
+      <c r="BH26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12891,12 +12891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="7" t="inlineStr">
+      <c r="BL26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12911,9 +12911,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12938,9 +12938,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12953,17 +12953,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12978,7 +12978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12988,12 +12988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13003,14 +13003,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -13028,27 +13028,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA27" s="7" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13063,22 +13063,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="7" t="inlineStr">
+      <c r="AD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13088,7 +13088,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="7" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13113,7 +13113,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="7" t="inlineStr">
+      <c r="AN27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13138,7 +13138,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="7" t="inlineStr">
+      <c r="AS27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13148,12 +13148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="7" t="inlineStr">
+      <c r="AU27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13163,22 +13163,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA27" s="7" t="inlineStr">
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13203,7 +13203,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF27" s="7" t="inlineStr">
+      <c r="BF27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13213,12 +13213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="7" t="inlineStr">
+      <c r="BH27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13233,12 +13233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="7" t="inlineStr">
+      <c r="BL27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13253,9 +13253,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13280,9 +13280,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13295,17 +13295,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13320,7 +13320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13330,12 +13330,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13345,14 +13345,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13370,27 +13370,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA28" s="7" t="inlineStr">
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13405,22 +13405,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG28" s="7" t="inlineStr">
+      <c r="AD28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13430,7 +13430,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="7" t="inlineStr">
+      <c r="AI28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13455,7 +13455,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN28" s="7" t="inlineStr">
+      <c r="AN28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13480,7 +13480,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS28" s="7" t="inlineStr">
+      <c r="AS28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13490,12 +13490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV28" s="7" t="inlineStr">
+      <c r="AU28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13505,22 +13505,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA28" s="7" t="inlineStr">
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13545,7 +13545,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF28" s="7" t="inlineStr">
+      <c r="BF28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13555,12 +13555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI28" s="7" t="inlineStr">
+      <c r="BH28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13575,12 +13575,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM28" s="7" t="inlineStr">
+      <c r="BL28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13595,9 +13595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13622,9 +13622,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13637,17 +13637,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13662,7 +13662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13672,29 +13672,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -13707,62 +13707,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="7" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13772,7 +13772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="7" t="inlineStr">
+      <c r="AI29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13797,7 +13797,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN29" s="7" t="inlineStr">
+      <c r="AN29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13822,7 +13822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS29" s="7" t="inlineStr">
+      <c r="AS29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13832,37 +13832,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA29" s="7" t="inlineStr">
+      <c r="AU29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13887,7 +13887,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF29" s="7" t="inlineStr">
+      <c r="BF29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13897,12 +13897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI29" s="7" t="inlineStr">
+      <c r="BH29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13917,12 +13917,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM29" s="7" t="inlineStr">
+      <c r="BL29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13937,9 +13937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13992,7 +13992,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WBA62PI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WBA62PI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14036,7 +14036,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WBA62PI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14058,20 +14058,1516 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>STM32WBA62PI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>STM32WBA62CI</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Supply Voltage (V) max</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32WBA6x.xlsx
+++ b/product_selector_out/STM32WBA6x.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7808,9 +7808,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7823,17 +7823,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7848,7 +7848,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7858,12 +7858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7873,14 +7873,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -7898,27 +7898,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7933,22 +7933,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7958,7 +7958,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7983,7 +7983,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8008,7 +8008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8018,12 +8018,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8033,22 +8033,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="8" t="inlineStr">
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8073,7 +8073,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF12" s="8" t="inlineStr">
+      <c r="BF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8083,12 +8083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8103,12 +8103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8123,9 +8123,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8150,9 +8150,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -8165,17 +8165,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8190,7 +8190,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8200,12 +8200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8215,14 +8215,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -8240,27 +8240,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8275,22 +8275,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8300,7 +8300,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8325,7 +8325,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8350,7 +8350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8360,12 +8360,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8375,22 +8375,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA13" s="8" t="inlineStr">
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8415,7 +8415,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF13" s="8" t="inlineStr">
+      <c r="BF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8425,12 +8425,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8445,12 +8445,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8465,9 +8465,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8492,9 +8492,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -8507,17 +8507,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8532,7 +8532,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8542,12 +8542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8557,14 +8557,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -8582,27 +8582,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8617,22 +8617,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8642,7 +8642,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8667,7 +8667,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8692,7 +8692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8702,12 +8702,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8717,22 +8717,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA14" s="8" t="inlineStr">
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8757,7 +8757,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF14" s="8" t="inlineStr">
+      <c r="BF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8767,12 +8767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8787,12 +8787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8807,9 +8807,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8834,9 +8834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8849,17 +8849,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8874,7 +8874,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8884,29 +8884,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -8919,62 +8919,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8984,32 +8984,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9034,7 +9034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9044,47 +9044,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9099,7 +9099,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF15" s="8" t="inlineStr">
+      <c r="BF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9109,12 +9109,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9129,12 +9129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9149,9 +9149,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9191,17 +9191,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9216,7 +9216,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9226,12 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9241,14 +9241,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -9266,27 +9266,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9301,22 +9301,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9326,7 +9326,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9351,7 +9351,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9376,7 +9376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9386,12 +9386,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9401,22 +9401,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA16" s="8" t="inlineStr">
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9441,7 +9441,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF16" s="8" t="inlineStr">
+      <c r="BF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9451,12 +9451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9471,12 +9471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9491,9 +9491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9518,9 +9518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -9533,17 +9533,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9558,7 +9558,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9568,29 +9568,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -9603,62 +9603,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9668,7 +9668,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9693,7 +9693,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9718,7 +9718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9728,37 +9728,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9783,7 +9783,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF17" s="8" t="inlineStr">
+      <c r="BF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9793,12 +9793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9813,12 +9813,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9833,9 +9833,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9875,17 +9875,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9900,7 +9900,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9910,12 +9910,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9950,27 +9950,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9985,22 +9985,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10010,7 +10010,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10035,7 +10035,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10060,7 +10060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10070,12 +10070,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10095,12 +10095,12 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AZ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA18" s="8" t="inlineStr">
+      <c r="AZ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10125,7 +10125,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF18" s="8" t="inlineStr">
+      <c r="BF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10135,12 +10135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10155,12 +10155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10202,9 +10202,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10217,17 +10217,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10242,7 +10242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10252,29 +10252,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -10287,62 +10287,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10352,7 +10352,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10377,7 +10377,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10402,7 +10402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10412,37 +10412,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10467,7 +10467,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF19" s="8" t="inlineStr">
+      <c r="BF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10477,12 +10477,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10497,12 +10497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10517,9 +10517,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10544,9 +10544,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10559,17 +10559,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10584,7 +10584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10594,12 +10594,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10609,14 +10609,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -10634,27 +10634,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10669,22 +10669,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10694,7 +10694,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10719,7 +10719,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10744,7 +10744,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10754,12 +10754,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10769,22 +10769,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA20" s="8" t="inlineStr">
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10809,7 +10809,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF20" s="8" t="inlineStr">
+      <c r="BF20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10819,12 +10819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10839,12 +10839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10859,9 +10859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10886,9 +10886,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10901,17 +10901,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10926,7 +10926,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10936,29 +10936,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -10971,62 +10971,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11036,32 +11036,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11086,7 +11086,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11096,47 +11096,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11151,7 +11151,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF21" s="8" t="inlineStr">
+      <c r="BF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11161,12 +11161,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11181,12 +11181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11201,9 +11201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11228,9 +11228,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11243,17 +11243,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11268,7 +11268,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11278,12 +11278,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11293,14 +11293,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -11318,27 +11318,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11353,22 +11353,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11378,7 +11378,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11403,7 +11403,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11428,7 +11428,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11438,37 +11438,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11493,7 +11493,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF22" s="8" t="inlineStr">
+      <c r="BF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11503,12 +11503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11523,12 +11523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11543,9 +11543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11570,9 +11570,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -11585,17 +11585,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11610,7 +11610,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11620,12 +11620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11635,14 +11635,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -11660,57 +11660,57 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11720,32 +11720,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11770,7 +11770,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11780,37 +11780,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11835,7 +11835,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF23" s="8" t="inlineStr">
+      <c r="BF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11845,12 +11845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11865,12 +11865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11885,9 +11885,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11912,9 +11912,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11927,17 +11927,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11952,7 +11952,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11962,12 +11962,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11977,14 +11977,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12002,27 +12002,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12037,22 +12037,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12062,7 +12062,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12087,7 +12087,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12112,7 +12112,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12122,12 +12122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12137,22 +12137,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA24" s="8" t="inlineStr">
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12177,7 +12177,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF24" s="8" t="inlineStr">
+      <c r="BF24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12187,12 +12187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12207,12 +12207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12254,9 +12254,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12269,17 +12269,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12294,7 +12294,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12304,29 +12304,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -12339,62 +12339,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12404,32 +12404,32 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AK25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AM25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AK25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AN25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12454,7 +12454,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12464,47 +12464,47 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12519,7 +12519,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF25" s="8" t="inlineStr">
+      <c r="BF25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12529,12 +12529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12549,12 +12549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12596,9 +12596,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -12611,17 +12611,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12636,7 +12636,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12646,12 +12646,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12661,14 +12661,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -12686,27 +12686,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA26" s="8" t="inlineStr">
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12721,22 +12721,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12746,7 +12746,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12771,7 +12771,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="8" t="inlineStr">
+      <c r="AN26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12796,7 +12796,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="8" t="inlineStr">
+      <c r="AS26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12806,12 +12806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="8" t="inlineStr">
+      <c r="AU26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12821,22 +12821,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA26" s="8" t="inlineStr">
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12861,7 +12861,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF26" s="8" t="inlineStr">
+      <c r="BF26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12871,12 +12871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="8" t="inlineStr">
+      <c r="BH26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12891,12 +12891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="8" t="inlineStr">
+      <c r="BL26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12911,9 +12911,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12938,9 +12938,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -12953,17 +12953,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12978,7 +12978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12988,12 +12988,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13003,14 +13003,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -13028,27 +13028,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA27" s="8" t="inlineStr">
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13063,22 +13063,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="8" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13088,7 +13088,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13113,7 +13113,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="inlineStr">
+      <c r="AN27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13138,7 +13138,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="8" t="inlineStr">
+      <c r="AS27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13148,12 +13148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="8" t="inlineStr">
+      <c r="AU27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13163,22 +13163,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA27" s="8" t="inlineStr">
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13203,7 +13203,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF27" s="8" t="inlineStr">
+      <c r="BF27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13213,12 +13213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="8" t="inlineStr">
+      <c r="BH27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13233,12 +13233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="8" t="inlineStr">
+      <c r="BL27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13253,9 +13253,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13280,9 +13280,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13295,17 +13295,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13320,7 +13320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13330,12 +13330,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13345,14 +13345,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13370,27 +13370,27 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA28" s="8" t="inlineStr">
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13405,22 +13405,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG28" s="8" t="inlineStr">
+      <c r="AD28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13430,7 +13430,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="8" t="inlineStr">
+      <c r="AI28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13455,7 +13455,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN28" s="8" t="inlineStr">
+      <c r="AN28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13480,7 +13480,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS28" s="8" t="inlineStr">
+      <c r="AS28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13490,12 +13490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV28" s="8" t="inlineStr">
+      <c r="AU28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13505,22 +13505,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA28" s="8" t="inlineStr">
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13545,7 +13545,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF28" s="8" t="inlineStr">
+      <c r="BF28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13555,12 +13555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI28" s="8" t="inlineStr">
+      <c r="BH28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13575,12 +13575,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM28" s="8" t="inlineStr">
+      <c r="BL28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13595,9 +13595,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13622,9 +13622,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -13637,17 +13637,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13662,7 +13662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13672,29 +13672,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -13707,62 +13707,62 @@
           <t>API</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="8" t="inlineStr">
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13772,7 +13772,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="8" t="inlineStr">
+      <c r="AI29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13797,7 +13797,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN29" s="8" t="inlineStr">
+      <c r="AN29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13822,7 +13822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS29" s="8" t="inlineStr">
+      <c r="AS29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13832,37 +13832,37 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA29" s="8" t="inlineStr">
+      <c r="AU29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13887,7 +13887,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BF29" s="8" t="inlineStr">
+      <c r="BF29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13897,12 +13897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BH29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI29" s="8" t="inlineStr">
+      <c r="BH29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13917,12 +13917,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM29" s="8" t="inlineStr">
+      <c r="BL29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13937,9 +13937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13992,7 +13992,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14036,7 +14036,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14058,7 +14058,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WBA62PI</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14072,1502 +14072,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
         <is>
           <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32WBA6x.xlsx
+++ b/product_selector_out/STM32WBA6x.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BQ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.59375" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1353,6 +1360,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2037,6 +2054,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2379,6 +2401,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3402,6 +3439,11 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
@@ -3747,6 +3789,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4089,6 +4136,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4431,6 +4483,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4773,6 +4830,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5115,6 +5177,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5457,6 +5524,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5799,6 +5871,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6141,6 +6218,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6483,6 +6565,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6825,6 +6912,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7167,9 +7259,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7192,14 +7289,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7217,6 +7313,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -7229,6 +7326,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -7269,7 +7367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BQ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7340,6 +7438,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7688,6 +7787,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7786,6 +7890,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8128,6 +8233,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -8470,6 +8580,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -8812,6 +8927,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -9154,6 +9274,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9496,6 +9621,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9838,6 +9968,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -10175,7 +10310,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10522,6 +10662,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -10864,6 +11009,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -11206,6 +11356,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11548,6 +11703,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -11890,6 +12050,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -12232,6 +12397,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12574,6 +12744,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -12916,6 +13091,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -13258,6 +13438,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13600,6 +13785,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -13942,11 +14132,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
